--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestStatusCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
